--- a/Exam/gymtrackerpro/lib/controller/__tests__/bbt/user-controller/createAdmin-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/bbt/user-controller/createAdmin-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="112">
-  <si>
-    <t>Statement: user-controller.createAdmin(data) – Server Action. Validates CreateAdminInput (email, fullName ≥8, phone, dateOfBirth, password ≥8). Delegates to userService.createAdmin(). Returns ActionResult&lt;AdminWithUser&gt;.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="53">
+  <si>
+    <t>Statement: createAdmin(data) – Validates the create-admin input and returns an ActionResult&lt;MemberWithUser&gt;. Returns success with the created admin on success. Returns a failure with the service error message for ConflictError and TransactionError.</t>
   </si>
   <si>
     <t/>
@@ -31,27 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: CreateAdminInput { email, fullName, phone, dateOfBirth, password }</t>
+    <t>Input: data: CreateAdminInput</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>userService.createAdmin is mock-injected</t>
+    <t>The created admin has role Role.ADMIN.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: ActionResult&lt;AdminWithUser&gt;</t>
+    <t>Output: Promise&lt;ActionResult&lt;MemberWithUser&gt;&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t xml:space="preserve">On success: AdminWithUser returned.
-On validation failure: errors returned.
-On AppError: message returned.</t>
+    <t>On success: admin created successfully, returned data has role ADMIN. On service error: operation fails with the service error message.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -66,40 +64,19 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>all fields valid</t>
-  </si>
-  <si>
-    <t>All fields pass schema</t>
-  </si>
-  <si>
-    <t>fullName length</t>
-  </si>
-  <si>
-    <t>fullName ≥ 8 chars</t>
-  </si>
-  <si>
-    <t>fullName &lt; 8 chars → validation error</t>
-  </si>
-  <si>
-    <t>email format</t>
-  </si>
-  <si>
-    <t>valid email</t>
-  </si>
-  <si>
-    <t>invalid email → validation error</t>
-  </si>
-  <si>
-    <t>service outcome</t>
-  </si>
-  <si>
-    <t>resolves AdminWithUser</t>
-  </si>
-  <si>
-    <t>throws ConflictError → failure with message</t>
-  </si>
-  <si>
-    <t>throws Error → generic failure</t>
+    <t>Input validity</t>
+  </si>
+  <si>
+    <t>All fields valid → admin created successfully, returned data has role ADMIN</t>
+  </si>
+  <si>
+    <t>Service error</t>
+  </si>
+  <si>
+    <t>An email conflict occurs → operation fails with message "Email taken"</t>
+  </si>
+  <si>
+    <t>A database transaction failure occurs → operation fails with message "DB failure"</t>
   </si>
   <si>
     <t>No TC</t>
@@ -117,46 +94,34 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>1,2,4,6</t>
-  </si>
-  <si>
-    <t>VALID_ADMIN_INPUT, service resolves AdminWithUser</t>
-  </si>
-  <si>
-    <t>{ success: true, data: AdminWithUser }</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>{ ...VALID_ADMIN_INPUT, fullName: "Jo" }</t>
-  </si>
-  <si>
-    <t>{ success: false, errors defined }</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>{ ...VALID_ADMIN_INPUT, email: "not-an-email" }</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>valid input, service throws ConflictError</t>
-  </si>
-  <si>
-    <t>{ success: false, message from error }</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>valid input, service throws Error</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "An unexpected error occurred" }</t>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>all required admin fields provided with valid values</t>
+  </si>
+  <si>
+    <t>admin created successfully, returned data has role ADMIN</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>all required admin fields provided with valid values, an email conflict occurs</t>
+  </si>
+  <si>
+    <t>operation fails with message "Email taken"</t>
+  </si>
+  <si>
+    <t>EC-3</t>
+  </si>
+  <si>
+    <t>all required admin fields provided with valid values, a database transaction failure occurs</t>
+  </si>
+  <si>
+    <t>operation fails with message "DB failure"</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -165,156 +130,15 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>fullName length boundary</t>
-  </si>
-  <si>
-    <t>fullName 7 chars → invalid</t>
-  </si>
-  <si>
-    <t>fullName 8 chars → valid</t>
-  </si>
-  <si>
-    <t>fullName boundary interior</t>
-  </si>
-  <si>
-    <t>fullName 9 chars → valid (min+1)</t>
-  </si>
-  <si>
-    <t>fullName 63 chars → valid (max-1)</t>
-  </si>
-  <si>
-    <t>password length boundary</t>
-  </si>
-  <si>
-    <t>password 9 chars → valid (min+1)</t>
-  </si>
-  <si>
-    <t>password 63 chars → valid (max-1)</t>
-  </si>
-  <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>fullName=7</t>
-  </si>
-  <si>
-    <t>fullName="1234567"</t>
-  </si>
-  <si>
-    <t>success=false, errors.fullName defined</t>
-  </si>
-  <si>
-    <t>fullName=8</t>
-  </si>
-  <si>
-    <t>fullName="12345678"</t>
-  </si>
-  <si>
-    <t>schema passes</t>
-  </si>
-  <si>
-    <t>fullName=9</t>
-  </si>
-  <si>
-    <t>fullName="AdminAcc1"</t>
-  </si>
-  <si>
-    <t>success=true</t>
-  </si>
-  <si>
-    <t>fullName=63</t>
-  </si>
-  <si>
-    <t>fullName="B".repeat(63)</t>
-  </si>
-  <si>
-    <t>password=9</t>
-  </si>
-  <si>
-    <t>password="Pass1@aAb"</t>
-  </si>
-  <si>
-    <t>password=63</t>
-  </si>
-  <si>
-    <t>password="A1@"+"a".repeat(60)</t>
-  </si>
-  <si>
     <t>TC from EC</t>
   </si>
   <si>
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
-  </si>
-  <si>
-    <t>Valid input, service resolves</t>
-  </si>
-  <si>
-    <t>success=true, AdminWithUser returned</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
-    <t>BVA-1</t>
-  </si>
-  <si>
-    <t>fullName 7 chars</t>
-  </si>
-  <si>
-    <t>success=false, errors defined</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
-    <t>Invalid email</t>
-  </si>
-  <si>
-    <t>EP-4</t>
-  </si>
-  <si>
-    <t>Service throws ConflictError</t>
-  </si>
-  <si>
-    <t>success=false, message from error</t>
-  </si>
-  <si>
-    <t>EP-5</t>
-  </si>
-  <si>
-    <t>Service throws unexpected Error</t>
-  </si>
-  <si>
-    <t>success=false, message="An unexpected error occurred"</t>
-  </si>
-  <si>
-    <t>BVA-3</t>
-  </si>
-  <si>
-    <t>fullName 9 chars</t>
-  </si>
-  <si>
-    <t>BVA-4</t>
-  </si>
-  <si>
-    <t>fullName 63 chars</t>
-  </si>
-  <si>
-    <t>BVA-5</t>
-  </si>
-  <si>
-    <t>password 9 chars</t>
-  </si>
-  <si>
-    <t>BVA-6</t>
-  </si>
-  <si>
-    <t>password 63 chars</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -345,16 +169,13 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>AUTH-06</t>
+    <t>CTRL-05</t>
   </si>
   <si>
     <t>n/a</t>
   </si>
   <si>
     <t>not yet</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -870,7 +691,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -914,10 +735,10 @@
         <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -925,83 +746,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1012,7 +763,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1024,19 +775,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1044,16 +795,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1061,16 +812,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1078,50 +829,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1132,7 +849,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1142,79 +859,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1225,7 +876,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1237,121 +888,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1362,7 +911,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1375,22 +924,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1398,19 +947,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1418,19 +967,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>81</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1438,139 +987,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1598,16 +1027,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1615,45 +1044,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>105</v>
+        <v>47</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>108</v>
+      <c r="A3" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="B3" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C3" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1662,19 +1091,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>109</v>
+        <v>51</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>111</v>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
